--- a/data/Trade Promo Brief Template - WK2 Catch it quick.xlsx
+++ b/data/Trade Promo Brief Template - WK2 Catch it quick.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27823"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ausdeloitte-my.sharepoint.com/personal/rodalmia_deloitte_com_au/Documents/Desktop/Work/Python/Greencross/Image-Web-Scraping/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greencrosslimited-my.sharepoint.com/personal/laura_scheetz_gxltd_com_au/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{6B65C777-CAF9-48AD-AA20-5441721EB015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7533CAB0-AD9E-41AD-B842-659CF860F99B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B65C777-CAF9-48AD-AA20-5441721EB015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16965" yWindow="-16530" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timeline" sheetId="7" r:id="rId1"/>
@@ -1753,10 +1753,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2864,8 +2864,8 @@
     <xf numFmtId="0" fontId="7" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="1" applyBorder="1"/>
@@ -2951,101 +2951,101 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3783,7 +3783,7 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AH57"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
     <col min="4" max="4" width="15.85546875" style="2" customWidth="1"/>
@@ -3798,49 +3798,49 @@
     <col min="17" max="31" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="184"/>
-      <c r="B1" s="183"/>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
-      <c r="F1" s="183" t="s">
+    <row r="1" spans="1:34">
+      <c r="A1" s="183"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="F1" s="182" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="183"/>
+      <c r="G1" s="182"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="O1" s="179" t="s">
+      <c r="O1" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="180"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="183"/>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="P1" s="179"/>
+    </row>
+    <row r="2" spans="1:34">
+      <c r="A2" s="182"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="O2" s="181" t="s">
+      <c r="O2" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="182"/>
-    </row>
-    <row r="3" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="190"/>
-      <c r="B3" s="191"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
+      <c r="P2" s="181"/>
+    </row>
+    <row r="3" spans="1:34" s="2" customFormat="1">
+      <c r="A3" s="189"/>
+      <c r="B3" s="190"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
       <c r="O3" s="22" t="s">
         <v>3</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34">
       <c r="F4" s="5" t="s">
         <v>5</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="48" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" ht="48">
       <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>19</v>
       </c>
       <c r="L5" s="7"/>
-      <c r="M5" s="185" t="s">
+      <c r="M5" s="184" t="s">
         <v>20</v>
       </c>
       <c r="O5" s="22" t="s">
@@ -3908,7 +3908,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="48" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" ht="48">
       <c r="F6" s="9" t="s">
         <v>23</v>
       </c>
@@ -3930,7 +3930,7 @@
       <c r="L6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="186"/>
+      <c r="M6" s="185"/>
       <c r="O6" s="22" t="s">
         <v>30</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" ht="24">
       <c r="F7" s="9" t="s">
         <v>32</v>
       </c>
@@ -3956,7 +3956,7 @@
       <c r="L7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="186"/>
+      <c r="M7" s="185"/>
       <c r="O7" s="22" t="s">
         <v>37</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" ht="24">
       <c r="F8" s="9" t="s">
         <v>39</v>
       </c>
@@ -3978,7 +3978,7 @@
       <c r="L8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="M8" s="186"/>
+      <c r="M8" s="185"/>
       <c r="O8" s="22" t="s">
         <v>42</v>
       </c>
@@ -3986,27 +3986,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" ht="21" customHeight="1">
       <c r="F9" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="188" t="s">
+      <c r="H9" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="188" t="s">
+      <c r="I9" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="188" t="s">
+      <c r="J9" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="188" t="s">
+      <c r="K9" s="187" t="s">
         <v>19</v>
       </c>
       <c r="L9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="186"/>
+      <c r="M9" s="185"/>
       <c r="O9" s="24" t="s">
         <v>49</v>
       </c>
@@ -4014,19 +4014,19 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" ht="24">
       <c r="F10" s="9" t="s">
         <v>51</v>
       </c>
       <c r="G10" s="11"/>
-      <c r="H10" s="189"/>
-      <c r="I10" s="189"/>
-      <c r="J10" s="189"/>
-      <c r="K10" s="189"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="188"/>
+      <c r="J10" s="188"/>
+      <c r="K10" s="188"/>
       <c r="L10" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="186"/>
+      <c r="M10" s="185"/>
       <c r="O10" s="22" t="s">
         <v>53</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="48" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" ht="48">
       <c r="F11" s="9" t="s">
         <v>55</v>
       </c>
@@ -4045,7 +4045,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
-      <c r="M11" s="187"/>
+      <c r="M11" s="186"/>
       <c r="O11" s="22" t="s">
         <v>57</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34">
       <c r="F12" s="12" t="s">
         <v>59</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34">
       <c r="F13" s="18"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -4101,7 +4101,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34">
       <c r="F14" s="18"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -4111,7 +4111,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34">
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
       <c r="H15" s="2"/>
@@ -4121,7 +4121,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34">
       <c r="F16" s="57"/>
       <c r="G16" s="85" t="s">
         <v>62</v>
@@ -4148,7 +4148,7 @@
       <c r="AG16" s="2"/>
       <c r="AH16" s="2"/>
     </row>
-    <row r="17" spans="5:34" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:34" ht="60">
       <c r="F17" s="77" t="s">
         <v>69</v>
       </c>
@@ -4169,7 +4169,7 @@
       <c r="AG17" s="2"/>
       <c r="AH17" s="2"/>
     </row>
-    <row r="18" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:34">
       <c r="E18" s="73"/>
       <c r="F18" s="30"/>
       <c r="G18" s="84"/>
@@ -4192,7 +4192,7 @@
       <c r="AG18" s="2"/>
       <c r="AH18" s="2"/>
     </row>
-    <row r="19" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:34">
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -4205,7 +4205,7 @@
       <c r="AG19" s="2"/>
       <c r="AH19" s="2"/>
     </row>
-    <row r="20" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:34">
       <c r="E20" s="73"/>
       <c r="F20" s="83"/>
       <c r="G20" s="85" t="s">
@@ -4233,7 +4233,7 @@
       <c r="AG20" s="2"/>
       <c r="AH20" s="2"/>
     </row>
-    <row r="21" spans="5:34" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:34" ht="60">
       <c r="F21" s="80" t="s">
         <v>73</v>
       </c>
@@ -4254,7 +4254,7 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
     </row>
-    <row r="22" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:34">
       <c r="F22" s="30"/>
       <c r="G22" s="29"/>
       <c r="H22" s="28"/>
@@ -4276,7 +4276,7 @@
       <c r="AG22" s="2"/>
       <c r="AH22" s="2"/>
     </row>
-    <row r="23" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:34">
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -4289,7 +4289,7 @@
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
     </row>
-    <row r="24" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:34">
       <c r="F24" s="83"/>
       <c r="G24" s="85" t="s">
         <v>62</v>
@@ -4316,7 +4316,7 @@
       <c r="AG24" s="2"/>
       <c r="AH24" s="2"/>
     </row>
-    <row r="25" spans="5:34" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:34" ht="60">
       <c r="F25" s="48" t="s">
         <v>76</v>
       </c>
@@ -4337,7 +4337,7 @@
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
     </row>
-    <row r="26" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:34">
       <c r="F26" s="30"/>
       <c r="G26" s="29"/>
       <c r="H26" s="28"/>
@@ -4359,7 +4359,7 @@
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
     </row>
-    <row r="27" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:34">
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -4369,7 +4369,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:34">
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -4379,7 +4379,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="5:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="5:34">
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4389,7 +4389,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="5:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:34" ht="15" customHeight="1">
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -4399,7 +4399,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="5:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="5:34" ht="15" customHeight="1">
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -4409,7 +4409,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="5:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:34" ht="15" customHeight="1">
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -4419,7 +4419,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:13" ht="15" customHeight="1">
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4429,7 +4429,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:13" ht="15" customHeight="1">
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4439,7 +4439,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:13" ht="15" customHeight="1">
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -4449,7 +4449,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:13" ht="15" customHeight="1">
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -4459,7 +4459,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:13" ht="15" customHeight="1">
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -4469,7 +4469,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:13" ht="15" customHeight="1">
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -4479,7 +4479,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:13" ht="15" customHeight="1">
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -4489,7 +4489,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:13" ht="15" customHeight="1">
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -4499,7 +4499,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:13" ht="15" customHeight="1">
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -4509,7 +4509,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:13" ht="15" customHeight="1">
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -4519,7 +4519,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="6:13" ht="15" customHeight="1">
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -4529,7 +4529,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:13" ht="15" customHeight="1">
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -4539,7 +4539,7 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:13" ht="15" customHeight="1">
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -4549,7 +4549,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="6:13" ht="15" customHeight="1">
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -4559,7 +4559,7 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
     </row>
-    <row r="47" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="6:13" ht="15" customHeight="1">
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -4569,7 +4569,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="6:13" ht="15" customHeight="1">
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -4579,7 +4579,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:13" ht="15" customHeight="1">
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -4589,7 +4589,7 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:13" ht="15" customHeight="1">
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4599,7 +4599,7 @@
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:13" ht="15" customHeight="1">
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4609,7 +4609,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:13" ht="15" customHeight="1">
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -4619,7 +4619,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:13" ht="15" customHeight="1">
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -4629,7 +4629,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:13" ht="15" customHeight="1">
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4639,7 +4639,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:13" ht="15" customHeight="1">
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4649,7 +4649,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:13" ht="15" customHeight="1">
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -4659,7 +4659,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="6:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:13" ht="15" customHeight="1">
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -4695,7 +4695,7 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE161"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
@@ -4706,73 +4706,73 @@
     <col min="7" max="31" width="9.140625" style="73"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="31.5">
       <c r="A1" s="43"/>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="201"/>
-      <c r="E1" s="201" t="s">
+      <c r="C1" s="191"/>
+      <c r="E1" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="201"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="202" t="s">
+      <c r="F1" s="191"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="B2" s="192" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="202"/>
-      <c r="E2" s="202" t="s">
+      <c r="C2" s="192"/>
+      <c r="E2" s="192" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="202"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="194" t="s">
+      <c r="F2" s="192"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" s="196" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="195"/>
+      <c r="C3" s="197"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="194" t="s">
+      <c r="E3" s="196" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="195"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="197" t="s">
+      <c r="F3" s="197"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75">
+      <c r="B4" s="193" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="198"/>
+      <c r="C4" s="194"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="198"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F4" s="194"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75">
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
       <c r="D5" s="2"/>
       <c r="E5" s="42"/>
       <c r="F5" s="42"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15.75">
       <c r="A6" s="74">
         <v>0</v>
       </c>
-      <c r="B6" s="196" t="s">
+      <c r="B6" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="196"/>
+      <c r="C6" s="195"/>
       <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="196" t="s">
+      <c r="E6" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="196"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F6" s="195"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75">
       <c r="A7" s="75" t="s">
         <v>84</v>
       </c>
@@ -4785,12 +4785,12 @@
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="199" t="s">
+      <c r="E7" s="198" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="200"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="199"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="75" t="s">
         <v>88</v>
       </c>
@@ -4801,25 +4801,25 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="192" t="s">
+      <c r="B9" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="193"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C9" s="201"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="192" t="s">
+      <c r="B10" s="200" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="193"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C10" s="201"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="75" t="s">
         <v>95</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" s="75" t="s">
         <v>98</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" s="75" t="s">
         <v>101</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" s="75" t="s">
         <v>104</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" s="75" t="s">
         <v>107</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" s="75" t="s">
         <v>110</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="75" t="s">
         <v>113</v>
       </c>
@@ -4896,36 +4896,36 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="194" t="s">
+    <row r="19" spans="1:3">
+      <c r="B19" s="196" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="195"/>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="197" t="s">
+      <c r="C19" s="197"/>
+    </row>
+    <row r="20" spans="1:3" ht="15.75">
+      <c r="B20" s="193" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="198"/>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C20" s="194"/>
+    </row>
+    <row r="21" spans="1:3" ht="15.75">
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15.75">
       <c r="A22" s="74">
         <v>0</v>
       </c>
-      <c r="B22" s="196" t="s">
+      <c r="B22" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="196"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="195"/>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="75" t="s">
         <v>84</v>
       </c>
@@ -4936,7 +4936,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="75" t="s">
         <v>88</v>
       </c>
@@ -4947,16 +4947,16 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="192" t="s">
+      <c r="B25" s="200" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="193"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="201"/>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="75" t="s">
         <v>93</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="75" t="s">
         <v>95</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="75" t="s">
         <v>98</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="75" t="s">
         <v>101</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="75" t="s">
         <v>104</v>
       </c>
@@ -5011,36 +5011,36 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="194" t="s">
+    <row r="32" spans="1:3">
+      <c r="B32" s="196" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="195"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="197" t="s">
+      <c r="C32" s="197"/>
+    </row>
+    <row r="33" spans="1:3" ht="15.75">
+      <c r="B33" s="193" t="s">
         <v>132</v>
       </c>
-      <c r="C33" s="198"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C33" s="194"/>
+    </row>
+    <row r="34" spans="1:3" ht="15.75">
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="15.75">
       <c r="A35" s="74">
         <v>0</v>
       </c>
-      <c r="B35" s="196" t="s">
+      <c r="B35" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="196"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="195"/>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="75" t="s">
         <v>84</v>
       </c>
@@ -5051,16 +5051,16 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="192" t="s">
+      <c r="B37" s="200" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="193"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="201"/>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="75" t="s">
         <v>93</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" s="75" t="s">
         <v>95</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" s="75" t="s">
         <v>98</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" s="75" t="s">
         <v>101</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="75" t="s">
         <v>104</v>
       </c>
@@ -5115,505 +5115,505 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:3">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:3">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:3">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:3">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:3">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:3">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:3">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:3">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:3">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:3">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:3">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:3">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:3">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:3">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:3">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:3">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:3">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:3">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:3">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:3">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:3">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:3">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:3">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:3">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:3">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:3">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:3">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:3">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:3">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:3">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:3">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
     </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:3">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
     </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:3">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
     </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:3">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:3">
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:3">
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
     </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:3">
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:3">
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:3">
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:3">
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:3">
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:3">
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:3">
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:3">
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:3">
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:3">
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:3">
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:3">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:3">
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:3">
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
     </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:3">
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
     </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:3">
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:3">
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:3">
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
     </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:3">
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
     </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:3">
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
     </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:3">
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
     </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:3">
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
     </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:3">
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
     </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:3">
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
     </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:3">
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
     </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:3">
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
     </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:3">
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
     </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:3">
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
     </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:3">
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
     </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:3">
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
     </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:3">
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
     </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:3">
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
     </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:3">
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
     </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:3">
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
     </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:3">
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
     </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:3">
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
     </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:3">
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
     </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:3">
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
     </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:3">
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
     </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:3">
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
     </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:3">
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
     </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:3">
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
     </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:3">
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
     </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:3">
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
     </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:3">
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
     </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:3">
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
     </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:3">
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
     </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:3">
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
     </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:3">
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
     </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:3">
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:3">
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E7 F3:F5 C3:C5 C21 B32:C34 C23:C24 C11:C18 C7:C8 C26:C30 B1:B30 C38:C1048576 C36 B35:B1048576" xr:uid="{4E168678-5D17-4F4F-9114-BE48A2237927}"/>
@@ -5628,7 +5628,7 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AA110"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="33" customWidth="1"/>
     <col min="2" max="2" width="10.140625" style="1" customWidth="1"/>
@@ -5650,13 +5650,13 @@
     <col min="18" max="27" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="203" t="s">
+    <row r="1" spans="1:21" ht="15" customHeight="1">
+      <c r="B1" s="202" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
       <c r="F1" s="31"/>
       <c r="G1" s="98" t="s">
         <v>142</v>
@@ -5671,11 +5671,11 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
+    <row r="2" spans="1:21">
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
       <c r="F2" s="31"/>
       <c r="G2" s="47" t="s">
         <v>69</v>
@@ -5690,13 +5690,13 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="205" t="s">
+    <row r="3" spans="1:21" ht="20.25" customHeight="1">
+      <c r="B3" s="204" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="41"/>
       <c r="G3" s="48" t="s">
         <v>145</v>
@@ -5711,7 +5711,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:21" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="35.25" customHeight="1">
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
       <c r="D4" s="20"/>
@@ -5724,7 +5724,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="10.5" customHeight="1">
       <c r="B5" s="64"/>
       <c r="C5" s="65"/>
       <c r="D5" s="20"/>
@@ -5736,24 +5736,24 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="11.25" customHeight="1">
       <c r="A6" s="33">
         <v>1</v>
       </c>
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="205" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
       <c r="G6" s="107"/>
       <c r="H6" s="107"/>
       <c r="I6" s="107"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="45">
       <c r="A7" s="33">
         <v>2</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21">
       <c r="A8" s="33">
         <v>3</v>
       </c>
@@ -5841,7 +5841,7 @@
       <c r="R8" s="69"/>
       <c r="S8" s="69"/>
     </row>
-    <row r="9" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="90">
       <c r="A9" s="33">
         <v>7</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="75">
       <c r="B10" s="36" t="s">
         <v>89</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="45">
       <c r="B11" s="36" t="s">
         <v>118</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="45">
       <c r="B12" s="36" t="s">
         <v>119</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="45">
       <c r="B13" s="36" t="s">
         <v>86</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="45">
       <c r="B14" s="36" t="s">
         <v>90</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21">
       <c r="A15" s="33">
         <v>6</v>
       </c>
@@ -6123,7 +6123,7 @@
       <c r="P15" s="120"/>
       <c r="Q15" s="120"/>
     </row>
-    <row r="16" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="30">
       <c r="B16" s="36" t="s">
         <v>96</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="60">
       <c r="A17" s="33">
         <v>5</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="30">
       <c r="B18" s="36" t="s">
         <v>134</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17">
       <c r="A19" s="33">
         <v>15</v>
       </c>
@@ -6275,7 +6275,7 @@
       <c r="P19" s="121"/>
       <c r="Q19" s="121"/>
     </row>
-    <row r="20" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" s="2" customFormat="1">
       <c r="A20" s="33">
         <v>16</v>
       </c>
@@ -6298,7 +6298,7 @@
       <c r="P20" s="70"/>
       <c r="Q20" s="70"/>
     </row>
-    <row r="21" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="45">
       <c r="A21" s="33">
         <v>17</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="45">
       <c r="B22" s="36" t="s">
         <v>103</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="45">
       <c r="B23" s="36" t="s">
         <v>121</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="45">
       <c r="B24" s="36" t="s">
         <v>122</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17">
       <c r="A25" s="33">
         <v>18</v>
       </c>
@@ -6484,7 +6484,7 @@
       <c r="P25" s="120"/>
       <c r="Q25" s="120"/>
     </row>
-    <row r="26" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="45">
       <c r="A26" s="33">
         <v>19</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="45">
       <c r="B27" s="39" t="s">
         <v>129</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="45">
       <c r="B28" s="39" t="s">
         <v>135</v>
       </c>
@@ -6607,7 +6607,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17">
       <c r="B29" s="88" t="s">
         <v>283</v>
       </c>
@@ -6627,7 +6627,7 @@
       <c r="P29" s="120"/>
       <c r="Q29" s="120"/>
     </row>
-    <row r="30" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="45">
       <c r="B30" s="39" t="s">
         <v>112</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="30">
       <c r="B31" s="39" t="s">
         <v>130</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17">
       <c r="A32" s="33">
         <v>20</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20">
       <c r="A33" s="33">
         <v>21</v>
       </c>
@@ -6777,7 +6777,7 @@
       <c r="P33" s="70"/>
       <c r="Q33" s="70"/>
     </row>
-    <row r="34" spans="1:20" s="33" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" s="33" customFormat="1" ht="90">
       <c r="A34" s="33">
         <v>22</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="35" spans="1:20" s="33" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" s="33" customFormat="1" ht="60">
       <c r="B35" s="60" t="s">
         <v>120</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="36" spans="1:20" s="33" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" s="33" customFormat="1" ht="60">
       <c r="B36" s="60" t="s">
         <v>133</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20">
       <c r="A37" s="33">
         <v>23</v>
       </c>
@@ -6938,7 +6938,7 @@
       <c r="P37" s="120"/>
       <c r="Q37" s="120"/>
     </row>
-    <row r="38" spans="1:20" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" s="2" customFormat="1" ht="75">
       <c r="A38" s="33">
         <v>24</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="39" spans="1:20" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" s="2" customFormat="1" ht="60">
       <c r="A39" s="33"/>
       <c r="B39" s="93" t="s">
         <v>100</v>
@@ -7031,7 +7031,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="40" spans="1:20" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" s="2" customFormat="1" ht="30">
       <c r="A40" s="33"/>
       <c r="B40" s="93" t="s">
         <v>127</v>
@@ -7070,7 +7070,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="41" spans="1:20" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" s="2" customFormat="1" ht="45">
       <c r="A41" s="33"/>
       <c r="B41" s="93" t="s">
         <v>128</v>
@@ -7111,7 +7111,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="42" spans="1:20" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" s="2" customFormat="1" ht="45">
       <c r="A42" s="33"/>
       <c r="B42" s="93" t="s">
         <v>136</v>
@@ -7152,7 +7152,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20">
       <c r="A43" s="33">
         <v>25</v>
       </c>
@@ -7173,7 +7173,7 @@
       <c r="P43" s="33"/>
       <c r="Q43" s="33"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20">
       <c r="A44" s="33">
         <v>31</v>
       </c>
@@ -7196,7 +7196,7 @@
       <c r="P44" s="70"/>
       <c r="Q44" s="70"/>
     </row>
-    <row r="45" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="45">
       <c r="A45" s="33">
         <v>32</v>
       </c>
@@ -7213,7 +7213,7 @@
       <c r="F45" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="G45" s="178" t="s">
+      <c r="G45" s="207" t="s">
         <v>350</v>
       </c>
       <c r="H45" s="36"/>
@@ -7239,7 +7239,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="30">
       <c r="A46" s="33">
         <v>33</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="45">
       <c r="A47" s="33">
         <v>34</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="45">
       <c r="B48" s="36" t="s">
         <v>109</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="45">
       <c r="B49" s="36" t="s">
         <v>123</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" ht="45">
       <c r="B50" s="36" t="s">
         <v>124</v>
       </c>
@@ -7439,7 +7439,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="45">
       <c r="B51" s="36" t="s">
         <v>125</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="30">
       <c r="B52" s="36" t="s">
         <v>126</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="45">
       <c r="B53" s="36" t="s">
         <v>137</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="45">
       <c r="B54" s="36" t="s">
         <v>138</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="30">
       <c r="B55" s="39" t="s">
         <v>139</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="45">
       <c r="B56" s="36" t="s">
         <v>140</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" ht="30">
       <c r="B57" s="115" t="s">
         <v>94</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" s="2" customFormat="1">
       <c r="A58" s="33">
         <v>35</v>
       </c>
@@ -7728,7 +7728,7 @@
       <c r="P58" s="121"/>
       <c r="Q58" s="121"/>
     </row>
-    <row r="59" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" s="2" customFormat="1">
       <c r="A59" s="33">
         <v>36</v>
       </c>
@@ -7751,7 +7751,7 @@
       <c r="P59" s="70"/>
       <c r="Q59" s="70"/>
     </row>
-    <row r="60" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" s="2" customFormat="1" ht="45">
       <c r="A60" s="33">
         <v>37</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" s="2" customFormat="1" ht="30">
       <c r="A61" s="33">
         <v>38</v>
       </c>
@@ -7829,13 +7829,13 @@
         <v>356</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" s="2" customFormat="1">
       <c r="A62" s="33"/>
       <c r="C62" s="31"/>
       <c r="F62" s="31"/>
       <c r="H62" s="31"/>
     </row>
-    <row r="63" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" s="2" customFormat="1">
       <c r="A63" s="33">
         <v>43</v>
       </c>
@@ -7858,7 +7858,7 @@
       <c r="P63" s="70"/>
       <c r="Q63" s="70"/>
     </row>
-    <row r="64" spans="1:17" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" s="2" customFormat="1" ht="30">
       <c r="A64" s="33">
         <v>44</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" s="2" customFormat="1" ht="30">
       <c r="A65" s="33"/>
       <c r="B65" s="60" t="s">
         <v>442</v>
@@ -7938,7 +7938,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" s="2" customFormat="1" ht="30">
       <c r="A66" s="33"/>
       <c r="B66" s="60" t="s">
         <v>445</v>
@@ -7977,7 +7977,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" s="2" customFormat="1" ht="30">
       <c r="A67" s="33"/>
       <c r="B67" s="60" t="s">
         <v>448</v>
@@ -8016,7 +8016,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" s="2" customFormat="1" ht="45">
       <c r="A68" s="33">
         <v>46</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" s="2" customFormat="1">
       <c r="A69" s="33"/>
       <c r="B69" s="60" t="s">
         <v>455</v>
@@ -8074,7 +8074,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" s="2" customFormat="1">
       <c r="A70" s="33">
         <v>47</v>
       </c>
@@ -8103,7 +8103,7 @@
       <c r="P70" s="72"/>
       <c r="Q70" s="72"/>
     </row>
-    <row r="71" spans="1:17" s="2" customFormat="1" ht="345" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" s="2" customFormat="1" ht="345">
       <c r="A71" s="33">
         <v>47</v>
       </c>
@@ -8136,7 +8136,7 @@
       <c r="P71" s="72"/>
       <c r="Q71" s="72"/>
     </row>
-    <row r="72" spans="1:17" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" s="33" customFormat="1">
       <c r="A72" s="33">
         <v>77</v>
       </c>
@@ -8157,7 +8157,7 @@
         <v xml:space="preserve">   ILCs:    Shop now: </v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17">
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
       <c r="D73" s="2"/>
@@ -8169,7 +8169,7 @@
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17">
       <c r="B74" s="31"/>
       <c r="C74" s="31"/>
       <c r="D74" s="2"/>
@@ -8181,7 +8181,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17">
       <c r="B75" s="31"/>
       <c r="C75" s="31"/>
       <c r="D75" s="2"/>
@@ -8193,7 +8193,7 @@
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17">
       <c r="B76" s="31"/>
       <c r="C76" s="31"/>
       <c r="D76" s="2"/>
@@ -8205,7 +8205,7 @@
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17">
       <c r="B77" s="31"/>
       <c r="C77" s="31"/>
       <c r="D77" s="2"/>
@@ -8217,7 +8217,7 @@
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17">
       <c r="B78" s="31"/>
       <c r="C78" s="31"/>
       <c r="D78" s="2"/>
@@ -8229,7 +8229,7 @@
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17">
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
       <c r="D79" s="2"/>
@@ -8241,7 +8241,7 @@
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17">
       <c r="B80" s="31"/>
       <c r="C80" s="31"/>
       <c r="D80" s="2"/>
@@ -8253,7 +8253,7 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:13">
       <c r="B81" s="31"/>
       <c r="C81" s="31"/>
       <c r="D81" s="2"/>
@@ -8265,7 +8265,7 @@
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:13">
       <c r="B82" s="31"/>
       <c r="C82" s="31"/>
       <c r="D82" s="2"/>
@@ -8277,7 +8277,7 @@
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:13">
       <c r="B83" s="31"/>
       <c r="C83" s="31"/>
       <c r="D83" s="2"/>
@@ -8289,7 +8289,7 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:13">
       <c r="B84" s="31"/>
       <c r="C84" s="31"/>
       <c r="D84" s="2"/>
@@ -8301,7 +8301,7 @@
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:13">
       <c r="B85" s="31"/>
       <c r="C85" s="31"/>
       <c r="D85" s="2"/>
@@ -8313,7 +8313,7 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:13">
       <c r="B86" s="31"/>
       <c r="C86" s="31"/>
       <c r="D86" s="2"/>
@@ -8325,7 +8325,7 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:13">
       <c r="B87" s="31"/>
       <c r="C87" s="31"/>
       <c r="D87" s="2"/>
@@ -8337,7 +8337,7 @@
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:13">
       <c r="B88" s="31"/>
       <c r="C88" s="31"/>
       <c r="D88" s="2"/>
@@ -8349,7 +8349,7 @@
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:13">
       <c r="B89" s="31"/>
       <c r="C89" s="31"/>
       <c r="D89" s="2"/>
@@ -8361,7 +8361,7 @@
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:13">
       <c r="B90" s="31"/>
       <c r="C90" s="31"/>
       <c r="D90" s="2"/>
@@ -8373,7 +8373,7 @@
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:13">
       <c r="B91" s="31"/>
       <c r="C91" s="31"/>
       <c r="D91" s="2"/>
@@ -8385,7 +8385,7 @@
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:13">
       <c r="B92" s="31"/>
       <c r="C92" s="31"/>
       <c r="D92" s="2"/>
@@ -8397,7 +8397,7 @@
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:13">
       <c r="B93" s="31"/>
       <c r="C93" s="31"/>
       <c r="D93" s="2"/>
@@ -8409,7 +8409,7 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:13">
       <c r="B94" s="31"/>
       <c r="C94" s="31"/>
       <c r="D94" s="2"/>
@@ -8421,7 +8421,7 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:13">
       <c r="B95" s="31"/>
       <c r="C95" s="31"/>
       <c r="D95" s="2"/>
@@ -8433,7 +8433,7 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:13">
       <c r="B96" s="31"/>
       <c r="C96" s="31"/>
       <c r="D96" s="2"/>
@@ -8445,7 +8445,7 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:13">
       <c r="B97" s="31"/>
       <c r="C97" s="31"/>
       <c r="D97" s="2"/>
@@ -8457,7 +8457,7 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:13">
       <c r="B98" s="31"/>
       <c r="C98" s="31"/>
       <c r="D98" s="2"/>
@@ -8469,7 +8469,7 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:13">
       <c r="B99" s="31"/>
       <c r="C99" s="31"/>
       <c r="D99" s="2"/>
@@ -8481,7 +8481,7 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:13">
       <c r="B100" s="31"/>
       <c r="C100" s="31"/>
       <c r="D100" s="2"/>
@@ -8493,7 +8493,7 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:13">
       <c r="B101" s="31"/>
       <c r="C101" s="31"/>
       <c r="D101" s="2"/>
@@ -8505,7 +8505,7 @@
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:13">
       <c r="B102" s="31"/>
       <c r="C102" s="31"/>
       <c r="D102" s="2"/>
@@ -8517,7 +8517,7 @@
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:13">
       <c r="B103" s="31"/>
       <c r="C103" s="31"/>
       <c r="D103" s="2"/>
@@ -8529,7 +8529,7 @@
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:13">
       <c r="B104" s="31"/>
       <c r="C104" s="31"/>
       <c r="D104" s="2"/>
@@ -8541,7 +8541,7 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:13">
       <c r="B105" s="31"/>
       <c r="C105" s="31"/>
       <c r="D105" s="2"/>
@@ -8553,7 +8553,7 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:13">
       <c r="B106" s="31"/>
       <c r="C106" s="31"/>
       <c r="D106" s="2"/>
@@ -8565,7 +8565,7 @@
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:13">
       <c r="B107" s="31"/>
       <c r="C107" s="31"/>
       <c r="D107" s="2"/>
@@ -8577,7 +8577,7 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:13">
       <c r="B108" s="31"/>
       <c r="C108" s="31"/>
       <c r="D108" s="2"/>
@@ -8589,7 +8589,7 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:13">
       <c r="B109" s="31"/>
       <c r="C109" s="31"/>
       <c r="D109" s="2"/>
@@ -8601,7 +8601,7 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:13">
       <c r="B110" s="31"/>
       <c r="C110" s="31"/>
       <c r="D110" s="2"/>
@@ -8744,7 +8744,7 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:AA69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="33" customWidth="1"/>
     <col min="2" max="2" width="10.140625" style="1" customWidth="1"/>
@@ -8766,13 +8766,13 @@
     <col min="18" max="27" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="203" t="s">
+    <row r="1" spans="1:21" ht="15" customHeight="1">
+      <c r="B1" s="202" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
       <c r="F1" s="31"/>
       <c r="G1" s="98" t="s">
         <v>142</v>
@@ -8787,11 +8787,11 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
+    <row r="2" spans="1:21">
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
       <c r="F2" s="31"/>
       <c r="G2" s="47" t="s">
         <v>69</v>
@@ -8806,13 +8806,13 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="205" t="s">
+    <row r="3" spans="1:21" ht="20.25" customHeight="1">
+      <c r="B3" s="204" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="41"/>
       <c r="G3" s="48" t="s">
         <v>145</v>
@@ -8827,7 +8827,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:21" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="35.25" customHeight="1">
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
       <c r="D4" s="20"/>
@@ -8840,7 +8840,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="10.5" customHeight="1">
       <c r="B5" s="64"/>
       <c r="C5" s="65"/>
       <c r="D5" s="20"/>
@@ -8852,24 +8852,24 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="11.25" customHeight="1">
       <c r="A6" s="33">
         <v>1</v>
       </c>
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="205" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
       <c r="G6" s="107"/>
       <c r="H6" s="107"/>
       <c r="I6" s="107"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="45">
       <c r="A7" s="33">
         <v>2</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="30">
       <c r="A8" s="33">
         <v>3</v>
       </c>
@@ -8975,7 +8975,7 @@
       <c r="R8" s="69"/>
       <c r="S8" s="69"/>
     </row>
-    <row r="9" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="90">
       <c r="A9" s="33">
         <v>7</v>
       </c>
@@ -9022,7 +9022,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="45">
       <c r="B10" s="36" t="s">
         <v>86</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="75">
       <c r="B11" s="36" t="s">
         <v>89</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="30">
       <c r="B12" s="39" t="s">
         <v>90</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="90">
       <c r="A13" s="33">
         <v>6</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="30">
       <c r="A14" s="33">
         <v>15</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="30">
       <c r="B15" s="36" t="s">
         <v>96</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="60">
       <c r="A16" s="33">
         <v>5</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" s="2" customFormat="1" ht="75">
       <c r="A17" s="33">
         <v>16</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="60">
       <c r="A18" s="33">
         <v>17</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="45">
       <c r="B19" s="36" t="s">
         <v>102</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="45">
       <c r="A20" s="33">
         <v>18</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="45">
       <c r="A21" s="33">
         <v>19</v>
       </c>
@@ -9515,7 +9515,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="30">
       <c r="B22" s="145" t="s">
         <v>106</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="45">
       <c r="B23" s="39" t="s">
         <v>108</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="45">
       <c r="A24" s="33">
         <v>20</v>
       </c>
@@ -9632,7 +9632,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="45">
       <c r="A25" s="33">
         <v>21</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="1:20" s="33" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" s="33" customFormat="1" ht="45">
       <c r="A26" s="33">
         <v>22</v>
       </c>
@@ -9727,7 +9727,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="27" spans="1:20" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" s="2" customFormat="1" ht="45">
       <c r="A27" s="33">
         <v>24</v>
       </c>
@@ -9766,7 +9766,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="28" spans="1:20" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" s="2" customFormat="1" ht="45">
       <c r="A28" s="33"/>
       <c r="B28" s="39" t="s">
         <v>114</v>
@@ -9812,7 +9812,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="30">
       <c r="A29" s="33">
         <v>25</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20">
       <c r="A30" s="33">
         <v>31</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="345">
       <c r="A31" s="33">
         <v>32</v>
       </c>
@@ -9907,7 +9907,7 @@
       <c r="P31" s="141"/>
       <c r="Q31" s="141"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20">
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
       <c r="D32" s="2"/>
@@ -9919,7 +9919,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13">
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="2"/>
@@ -9931,7 +9931,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13">
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="2"/>
@@ -9943,7 +9943,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13">
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
       <c r="D35" s="2"/>
@@ -9955,7 +9955,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13">
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
       <c r="D36" s="2"/>
@@ -9967,7 +9967,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13">
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
       <c r="D37" s="2"/>
@@ -9979,7 +9979,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13">
       <c r="B38" s="31"/>
       <c r="C38" s="31"/>
       <c r="D38" s="2"/>
@@ -9991,7 +9991,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13">
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
       <c r="D39" s="2"/>
@@ -10003,7 +10003,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13">
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
       <c r="D40" s="2"/>
@@ -10015,7 +10015,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13">
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
       <c r="D41" s="2"/>
@@ -10027,7 +10027,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:13">
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
       <c r="D42" s="2"/>
@@ -10039,7 +10039,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13">
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
       <c r="D43" s="2"/>
@@ -10051,7 +10051,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13">
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
       <c r="D44" s="2"/>
@@ -10063,7 +10063,7 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13">
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
       <c r="D45" s="2"/>
@@ -10075,7 +10075,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13">
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
       <c r="D46" s="2"/>
@@ -10087,7 +10087,7 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:13">
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
       <c r="D47" s="2"/>
@@ -10099,7 +10099,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13">
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
       <c r="D48" s="2"/>
@@ -10111,7 +10111,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13">
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
       <c r="D49" s="2"/>
@@ -10123,7 +10123,7 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13">
       <c r="B50" s="31"/>
       <c r="C50" s="31"/>
       <c r="D50" s="2"/>
@@ -10135,7 +10135,7 @@
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13">
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
       <c r="D51" s="2"/>
@@ -10147,7 +10147,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13">
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
       <c r="D52" s="2"/>
@@ -10159,7 +10159,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13">
       <c r="B53" s="31"/>
       <c r="C53" s="31"/>
       <c r="D53" s="2"/>
@@ -10171,7 +10171,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13">
       <c r="B54" s="31"/>
       <c r="C54" s="31"/>
       <c r="D54" s="2"/>
@@ -10183,7 +10183,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13">
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
       <c r="D55" s="2"/>
@@ -10195,7 +10195,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13">
       <c r="B56" s="31"/>
       <c r="C56" s="31"/>
       <c r="D56" s="2"/>
@@ -10207,7 +10207,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13">
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
       <c r="D57" s="2"/>
@@ -10219,7 +10219,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13">
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
       <c r="D58" s="2"/>
@@ -10231,7 +10231,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13">
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
       <c r="D59" s="2"/>
@@ -10243,7 +10243,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13">
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
       <c r="D60" s="2"/>
@@ -10255,7 +10255,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13">
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
       <c r="D61" s="2"/>
@@ -10267,7 +10267,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13">
       <c r="B62" s="31"/>
       <c r="C62" s="31"/>
       <c r="D62" s="2"/>
@@ -10279,7 +10279,7 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13">
       <c r="B63" s="31"/>
       <c r="C63" s="31"/>
       <c r="D63" s="2"/>
@@ -10291,7 +10291,7 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13">
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
       <c r="D64" s="2"/>
@@ -10303,7 +10303,7 @@
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:13">
       <c r="B65" s="31"/>
       <c r="C65" s="31"/>
       <c r="D65" s="2"/>
@@ -10315,7 +10315,7 @@
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:13">
       <c r="B66" s="31"/>
       <c r="C66" s="31"/>
       <c r="D66" s="2"/>
@@ -10327,7 +10327,7 @@
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:13">
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
       <c r="D67" s="2"/>
@@ -10339,7 +10339,7 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:13">
       <c r="B68" s="31"/>
       <c r="C68" s="31"/>
       <c r="D68" s="2"/>
@@ -10351,7 +10351,7 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:13">
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
       <c r="D69" s="2"/>
@@ -10443,7 +10443,7 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="33" customWidth="1"/>
     <col min="2" max="2" width="10.140625" style="1" customWidth="1"/>
@@ -10465,13 +10465,13 @@
     <col min="18" max="27" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="203" t="s">
+    <row r="1" spans="1:21" ht="15" customHeight="1">
+      <c r="B1" s="202" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
       <c r="F1" s="31"/>
       <c r="G1" s="98" t="s">
         <v>142</v>
@@ -10486,11 +10486,11 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
+    <row r="2" spans="1:21">
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
       <c r="F2" s="31"/>
       <c r="G2" s="47" t="s">
         <v>69</v>
@@ -10505,13 +10505,13 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="205" t="s">
+    <row r="3" spans="1:21" ht="20.25" customHeight="1">
+      <c r="B3" s="204" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="41"/>
       <c r="G3" s="48" t="s">
         <v>145</v>
@@ -10526,7 +10526,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:21" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="35.25" customHeight="1">
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
       <c r="D4" s="20"/>
@@ -10539,7 +10539,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="10.5" customHeight="1">
       <c r="B5" s="64"/>
       <c r="C5" s="65"/>
       <c r="D5" s="20"/>
@@ -10551,24 +10551,24 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="11.25" customHeight="1">
       <c r="A6" s="33">
         <v>1</v>
       </c>
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="205" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
       <c r="G6" s="107"/>
       <c r="H6" s="107"/>
       <c r="I6" s="107"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="45">
       <c r="A7" s="33">
         <v>2</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="30">
       <c r="A8" s="33">
         <v>7</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="90">
       <c r="B9" s="36" t="s">
         <v>85</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="45">
       <c r="B10" s="36" t="s">
         <v>118</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="75">
       <c r="B11" s="36" t="s">
         <v>89</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="45">
       <c r="B12" s="36" t="s">
         <v>119</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" s="2" customFormat="1" ht="60">
       <c r="A13" s="33">
         <v>16</v>
       </c>
@@ -10887,7 +10887,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="45">
       <c r="A14" s="33">
         <v>17</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="45">
       <c r="B15" s="36" t="s">
         <v>122</v>
       </c>
@@ -10970,7 +10970,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="45">
       <c r="B16" s="36" t="s">
         <v>123</v>
       </c>
@@ -11010,7 +11010,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="45">
       <c r="A17" s="33">
         <v>19</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="45">
       <c r="B18" s="145" t="s">
         <v>125</v>
       </c>
@@ -11095,7 +11095,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="30">
       <c r="B19" s="39" t="s">
         <v>126</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="30">
       <c r="A20" s="33">
         <v>21</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="33" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" s="33" customFormat="1" ht="45">
       <c r="B21" s="46" t="s">
         <v>128</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" s="2" customFormat="1" ht="45">
       <c r="A22" s="33">
         <v>24</v>
       </c>
@@ -11266,7 +11266,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="30">
       <c r="A23" s="33">
         <v>31</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24" s="33">
         <v>32</v>
       </c>
@@ -11336,7 +11336,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="45">
       <c r="B25" s="60" t="s">
         <v>450</v>
       </c>
@@ -11366,7 +11366,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="345" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="345">
       <c r="B26" s="60" t="s">
         <v>459</v>
       </c>
@@ -11396,7 +11396,7 @@
       <c r="P26" s="141"/>
       <c r="Q26" s="141"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
       <c r="D27" s="2"/>
@@ -11408,7 +11408,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
       <c r="D28" s="2"/>
@@ -11420,7 +11420,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
       <c r="D29" s="2"/>
@@ -11432,7 +11432,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19">
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="2"/>
@@ -11444,7 +11444,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19">
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="2"/>
@@ -11456,7 +11456,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
       <c r="D32" s="2"/>
@@ -11468,7 +11468,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13">
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="2"/>
@@ -11480,7 +11480,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13">
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="2"/>
@@ -11492,7 +11492,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13">
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
       <c r="D35" s="2"/>
@@ -11504,7 +11504,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13">
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
       <c r="D36" s="2"/>
@@ -11516,7 +11516,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13">
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
       <c r="D37" s="2"/>
@@ -11528,7 +11528,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13">
       <c r="B38" s="31"/>
       <c r="C38" s="31"/>
       <c r="D38" s="2"/>
@@ -11540,7 +11540,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13">
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
       <c r="D39" s="2"/>
@@ -11552,7 +11552,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13">
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
       <c r="D40" s="2"/>
@@ -11564,7 +11564,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13">
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
       <c r="D41" s="2"/>
@@ -11576,7 +11576,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:13">
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
       <c r="D42" s="2"/>
@@ -11588,7 +11588,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13">
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
       <c r="D43" s="2"/>
@@ -11600,7 +11600,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13">
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
       <c r="D44" s="2"/>
@@ -11612,7 +11612,7 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13">
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
       <c r="D45" s="2"/>
@@ -11624,7 +11624,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13">
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
       <c r="D46" s="2"/>
@@ -11636,7 +11636,7 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:13">
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
       <c r="D47" s="2"/>
@@ -11648,7 +11648,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13">
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
       <c r="D48" s="2"/>
@@ -11660,7 +11660,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13">
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
       <c r="D49" s="2"/>
@@ -11672,7 +11672,7 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13">
       <c r="B50" s="31"/>
       <c r="C50" s="31"/>
       <c r="D50" s="2"/>
@@ -11684,7 +11684,7 @@
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13">
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
       <c r="D51" s="2"/>
@@ -11696,7 +11696,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13">
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
       <c r="D52" s="2"/>
@@ -11708,7 +11708,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13">
       <c r="B53" s="31"/>
       <c r="C53" s="31"/>
       <c r="D53" s="2"/>
@@ -11720,7 +11720,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13">
       <c r="B54" s="31"/>
       <c r="C54" s="31"/>
       <c r="D54" s="2"/>
@@ -11732,7 +11732,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13">
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
       <c r="D55" s="2"/>
@@ -11744,7 +11744,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13">
       <c r="B56" s="31"/>
       <c r="C56" s="31"/>
       <c r="D56" s="2"/>
@@ -11756,7 +11756,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13">
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
       <c r="D57" s="2"/>
@@ -11768,7 +11768,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13">
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
       <c r="D58" s="2"/>
@@ -11780,7 +11780,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13">
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
       <c r="D59" s="2"/>
@@ -11792,7 +11792,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13">
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
       <c r="D60" s="2"/>
@@ -11804,7 +11804,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13">
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
       <c r="D61" s="2"/>
@@ -11894,7 +11894,7 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:AA62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="33" customWidth="1"/>
     <col min="2" max="2" width="10.140625" style="1" customWidth="1"/>
@@ -11916,13 +11916,13 @@
     <col min="18" max="27" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="203" t="s">
+    <row r="1" spans="1:21" ht="15" customHeight="1">
+      <c r="B1" s="202" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
       <c r="F1" s="31"/>
       <c r="G1" s="98" t="s">
         <v>142</v>
@@ -11937,11 +11937,11 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
+    <row r="2" spans="1:21">
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
       <c r="F2" s="31"/>
       <c r="G2" s="47" t="s">
         <v>69</v>
@@ -11956,13 +11956,13 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="205" t="s">
+    <row r="3" spans="1:21" ht="20.25" customHeight="1">
+      <c r="B3" s="204" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="41"/>
       <c r="G3" s="48" t="s">
         <v>145</v>
@@ -11977,7 +11977,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:21" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="35.25" customHeight="1">
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
       <c r="D4" s="20"/>
@@ -11990,7 +11990,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="10.5" customHeight="1">
       <c r="B5" s="64"/>
       <c r="C5" s="65"/>
       <c r="D5" s="20"/>
@@ -12002,24 +12002,24 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="11.25" customHeight="1">
       <c r="A6" s="33">
         <v>1</v>
       </c>
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="205" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
       <c r="G6" s="107"/>
       <c r="H6" s="107"/>
       <c r="I6" s="107"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="45">
       <c r="A7" s="33">
         <v>2</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="30">
       <c r="A8" s="33">
         <v>3</v>
       </c>
@@ -12125,7 +12125,7 @@
       <c r="R8" s="69"/>
       <c r="S8" s="69"/>
     </row>
-    <row r="9" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="45">
       <c r="B9" s="36" t="s">
         <v>86</v>
       </c>
@@ -12167,7 +12167,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="45">
       <c r="B10" s="36" t="s">
         <v>90</v>
       </c>
@@ -12209,7 +12209,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="60">
       <c r="A11" s="33">
         <v>6</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="30">
       <c r="B12" s="36" t="s">
         <v>96</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="60">
       <c r="A13" s="33">
         <v>5</v>
       </c>
@@ -12339,7 +12339,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="30">
       <c r="B14" s="36" t="s">
         <v>134</v>
       </c>
@@ -12383,7 +12383,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="45">
       <c r="A15" s="33">
         <v>15</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" s="2" customFormat="1" ht="45">
       <c r="A16" s="33">
         <v>16</v>
       </c>
@@ -12469,7 +12469,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="45">
       <c r="B17" s="39" t="s">
         <v>112</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="45">
       <c r="A18" s="33">
         <v>18</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="45">
       <c r="B19" s="39" t="s">
         <v>138</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="30">
       <c r="B20" s="145" t="s">
         <v>139</v>
       </c>
@@ -12630,7 +12630,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="45">
       <c r="A21" s="33">
         <v>21</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" s="33" customFormat="1">
       <c r="B22" s="60" t="s">
         <v>455</v>
       </c>
@@ -12702,7 +12702,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="45">
       <c r="A23" s="33">
         <v>23</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="2" customFormat="1" ht="345" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" s="2" customFormat="1" ht="345">
       <c r="A24" s="33"/>
       <c r="B24" s="95" t="s">
         <v>459</v>
@@ -12766,7 +12766,7 @@
       <c r="P24" s="130"/>
       <c r="Q24" s="130"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18">
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="2"/>
@@ -12778,7 +12778,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18">
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="2"/>
@@ -12790,7 +12790,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18">
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
       <c r="D27" s="2"/>
@@ -12802,7 +12802,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18">
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
       <c r="D28" s="2"/>
@@ -12814,7 +12814,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18">
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
       <c r="D29" s="2"/>
@@ -12826,7 +12826,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18">
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="2"/>
@@ -12838,7 +12838,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18">
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="2"/>
@@ -12850,7 +12850,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18">
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
       <c r="D32" s="2"/>
@@ -12862,7 +12862,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13">
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="2"/>
@@ -12874,7 +12874,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13">
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="2"/>
@@ -12886,7 +12886,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13">
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
       <c r="D35" s="2"/>
@@ -12898,7 +12898,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13">
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
       <c r="D36" s="2"/>
@@ -12910,7 +12910,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13">
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
       <c r="D37" s="2"/>
@@ -12922,7 +12922,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13">
       <c r="B38" s="31"/>
       <c r="C38" s="31"/>
       <c r="D38" s="2"/>
@@ -12934,7 +12934,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13">
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
       <c r="D39" s="2"/>
@@ -12946,7 +12946,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13">
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
       <c r="D40" s="2"/>
@@ -12958,7 +12958,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13">
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
       <c r="D41" s="2"/>
@@ -12970,7 +12970,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:13">
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
       <c r="D42" s="2"/>
@@ -12982,7 +12982,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13">
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
       <c r="D43" s="2"/>
@@ -12994,7 +12994,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13">
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
       <c r="D44" s="2"/>
@@ -13006,7 +13006,7 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13">
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
       <c r="D45" s="2"/>
@@ -13018,7 +13018,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13">
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
       <c r="D46" s="2"/>
@@ -13030,7 +13030,7 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:13">
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
       <c r="D47" s="2"/>
@@ -13042,7 +13042,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13">
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
       <c r="D48" s="2"/>
@@ -13054,7 +13054,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13">
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
       <c r="D49" s="2"/>
@@ -13066,7 +13066,7 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13">
       <c r="B50" s="31"/>
       <c r="C50" s="31"/>
       <c r="D50" s="2"/>
@@ -13078,7 +13078,7 @@
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13">
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
       <c r="D51" s="2"/>
@@ -13090,7 +13090,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13">
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
       <c r="D52" s="2"/>
@@ -13102,7 +13102,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13">
       <c r="B53" s="31"/>
       <c r="C53" s="31"/>
       <c r="D53" s="2"/>
@@ -13114,7 +13114,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13">
       <c r="B54" s="31"/>
       <c r="C54" s="31"/>
       <c r="D54" s="2"/>
@@ -13126,7 +13126,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13">
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
       <c r="D55" s="2"/>
@@ -13138,7 +13138,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13">
       <c r="B56" s="31"/>
       <c r="C56" s="31"/>
       <c r="D56" s="2"/>
@@ -13150,7 +13150,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13">
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
       <c r="D57" s="2"/>
@@ -13162,7 +13162,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13">
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
       <c r="D58" s="2"/>
@@ -13174,7 +13174,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13">
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
       <c r="D59" s="2"/>
@@ -13186,7 +13186,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13">
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
       <c r="D60" s="2"/>
@@ -13198,7 +13198,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13">
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
       <c r="D61" s="2"/>
@@ -13210,7 +13210,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13">
       <c r="B62" s="31"/>
       <c r="C62" s="31"/>
       <c r="D62" s="2"/>
@@ -13288,7 +13288,7 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:AA49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="33" customWidth="1"/>
     <col min="2" max="2" width="10.140625" style="1" customWidth="1"/>
@@ -13310,13 +13310,13 @@
     <col min="18" max="27" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="203" t="s">
+    <row r="1" spans="1:21" ht="15" customHeight="1">
+      <c r="B1" s="202" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
       <c r="F1" s="31"/>
       <c r="G1" s="98" t="s">
         <v>142</v>
@@ -13331,11 +13331,11 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
+    <row r="2" spans="1:21">
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
       <c r="F2" s="31"/>
       <c r="G2" s="47" t="s">
         <v>69</v>
@@ -13350,13 +13350,13 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="205" t="s">
+    <row r="3" spans="1:21" ht="20.25" customHeight="1">
+      <c r="B3" s="204" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
       <c r="F3" s="41"/>
       <c r="G3" s="48" t="s">
         <v>145</v>
@@ -13371,7 +13371,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:21" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="35.25" customHeight="1">
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
       <c r="D4" s="20"/>
@@ -13384,7 +13384,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="10.5" customHeight="1">
       <c r="B5" s="64"/>
       <c r="C5" s="65"/>
       <c r="D5" s="20"/>
@@ -13396,24 +13396,24 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="11.25" customHeight="1">
       <c r="A6" s="33">
         <v>1</v>
       </c>
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="205" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
       <c r="G6" s="107"/>
       <c r="H6" s="107"/>
       <c r="I6" s="107"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="45">
       <c r="A7" s="33">
         <v>2</v>
       </c>
@@ -13476,7 +13476,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" s="2" customFormat="1" ht="30">
       <c r="A8" s="33"/>
       <c r="B8" s="60" t="s">
         <v>448</v>
@@ -13515,7 +13515,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" s="2" customFormat="1">
       <c r="A9" s="33">
         <v>47</v>
       </c>
@@ -13544,7 +13544,7 @@
       <c r="P9" s="141"/>
       <c r="Q9" s="141"/>
     </row>
-    <row r="10" spans="1:21" s="2" customFormat="1" ht="345" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" s="2" customFormat="1" ht="345">
       <c r="A10" s="33">
         <v>47</v>
       </c>
@@ -13577,7 +13577,7 @@
       <c r="P10" s="141"/>
       <c r="Q10" s="141"/>
     </row>
-    <row r="11" spans="1:21" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" s="33" customFormat="1">
       <c r="A11" s="33">
         <v>77</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v xml:space="preserve">   ILCs:    Shop now: </v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21">
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
       <c r="D12" s="2"/>
@@ -13610,7 +13610,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21">
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
       <c r="D13" s="2"/>
@@ -13622,7 +13622,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21">
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
       <c r="D14" s="2"/>
@@ -13634,7 +13634,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21">
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
       <c r="D15" s="2"/>
@@ -13646,7 +13646,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21">
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
       <c r="D16" s="2"/>
@@ -13658,7 +13658,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13">
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
       <c r="D17" s="2"/>
@@ -13670,7 +13670,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13">
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="2"/>
@@ -13682,7 +13682,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13">
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
       <c r="D19" s="2"/>
@@ -13694,7 +13694,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13">
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
       <c r="D20" s="2"/>
@@ -13706,7 +13706,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13">
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
       <c r="D21" s="2"/>
@@ -13718,7 +13718,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13">
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
       <c r="D22" s="2"/>
@@ -13730,7 +13730,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13">
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
       <c r="D23" s="2"/>
@@ -13742,7 +13742,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13">
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
       <c r="D24" s="2"/>
@@ -13754,7 +13754,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13">
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="2"/>
@@ -13766,7 +13766,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13">
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="2"/>
@@ -13778,7 +13778,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13">
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
       <c r="D27" s="2"/>
@@ -13790,7 +13790,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13">
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
       <c r="D28" s="2"/>
@@ -13802,7 +13802,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13">
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
       <c r="D29" s="2"/>
@@ -13814,7 +13814,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13">
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="2"/>
@@ -13826,7 +13826,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13">
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="2"/>
@@ -13838,7 +13838,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13">
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
       <c r="D32" s="2"/>
@@ -13850,7 +13850,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13">
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="2"/>
@@ -13862,7 +13862,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13">
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="2"/>
@@ -13874,7 +13874,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13">
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
       <c r="D35" s="2"/>
@@ -13886,7 +13886,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13">
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
       <c r="D36" s="2"/>
@@ -13898,7 +13898,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13">
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
       <c r="D37" s="2"/>
@@ -13910,7 +13910,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13">
       <c r="B38" s="31"/>
       <c r="C38" s="31"/>
       <c r="D38" s="2"/>
@@ -13922,7 +13922,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13">
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
       <c r="D39" s="2"/>
@@ -13934,7 +13934,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13">
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
       <c r="D40" s="2"/>
@@ -13946,7 +13946,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13">
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
       <c r="D41" s="2"/>
@@ -13958,7 +13958,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:13">
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
       <c r="D42" s="2"/>
@@ -13970,7 +13970,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13">
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
       <c r="D43" s="2"/>
@@ -13982,7 +13982,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13">
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
       <c r="D44" s="2"/>
@@ -13994,7 +13994,7 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13">
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
       <c r="D45" s="2"/>
@@ -14006,7 +14006,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13">
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
       <c r="D46" s="2"/>
@@ -14018,7 +14018,7 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:13">
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
       <c r="D47" s="2"/>
@@ -14030,7 +14030,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13">
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
       <c r="D48" s="2"/>
@@ -14042,7 +14042,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13">
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
       <c r="D49" s="2"/>
@@ -14089,7 +14089,7 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AF56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
     <col min="2" max="2" width="16.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -14102,48 +14102,48 @@
     <col min="9" max="32" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B1" s="207" t="s">
+    <row r="1" spans="2:12" ht="21">
+      <c r="B1" s="206" t="s">
         <v>462</v>
       </c>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
       <c r="H1" s="20"/>
       <c r="I1" s="20"/>
       <c r="J1" s="20"/>
       <c r="K1" s="20"/>
       <c r="L1" s="20"/>
     </row>
-    <row r="2" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="207"/>
+    <row r="2" spans="2:12" ht="21">
+      <c r="B2" s="206"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
+      <c r="G2" s="206"/>
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
+    <row r="3" spans="2:12" ht="21">
+      <c r="B3" s="206"/>
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="206"/>
+      <c r="F3" s="206"/>
+      <c r="G3" s="206"/>
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
       <c r="L3" s="20"/>
     </row>
-    <row r="4" spans="2:12" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" s="2" customFormat="1" ht="21">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -14156,7 +14156,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12">
       <c r="B5" s="49" t="s">
         <v>463</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="75">
       <c r="B6" s="50" t="s">
         <v>470</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="75">
       <c r="B7" s="50" t="s">
         <v>44</v>
       </c>
@@ -14221,7 +14221,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="75">
       <c r="B8" s="50" t="s">
         <v>44</v>
       </c>
@@ -14242,7 +14242,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="75">
       <c r="B9" s="55" t="s">
         <v>44</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="75">
       <c r="B10" s="54" t="s">
         <v>44</v>
       </c>
@@ -14284,7 +14284,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="75">
       <c r="B11" s="54" t="s">
         <v>44</v>
       </c>
@@ -14305,7 +14305,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="75">
       <c r="B12" s="54" t="s">
         <v>44</v>
       </c>
@@ -14324,7 +14324,7 @@
       <c r="G12" s="109"/>
       <c r="H12" s="109"/>
     </row>
-    <row r="13" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="75">
       <c r="B13" s="54" t="s">
         <v>44</v>
       </c>
@@ -14345,7 +14345,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="75">
       <c r="B14" s="55" t="s">
         <v>44</v>
       </c>
@@ -14366,7 +14366,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="75">
       <c r="B15" s="50" t="s">
         <v>44</v>
       </c>
@@ -14387,7 +14387,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="75">
       <c r="B16" s="50" t="s">
         <v>44</v>
       </c>
@@ -14408,7 +14408,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" ht="75">
       <c r="B17" s="55" t="s">
         <v>44</v>
       </c>
@@ -14429,7 +14429,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="75">
       <c r="B18" s="54" t="s">
         <v>44</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" ht="75">
       <c r="B19" s="54" t="s">
         <v>44</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" ht="75">
       <c r="B20" s="54" t="s">
         <v>44</v>
       </c>
@@ -14490,7 +14490,7 @@
       <c r="G20" s="50"/>
       <c r="H20" s="109"/>
     </row>
-    <row r="21" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" ht="75">
       <c r="B21" s="112" t="s">
         <v>44</v>
       </c>
@@ -14509,7 +14509,7 @@
       <c r="G21" s="50"/>
       <c r="H21" s="109"/>
     </row>
-    <row r="22" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" ht="75">
       <c r="B22" s="55" t="s">
         <v>504</v>
       </c>
@@ -14528,7 +14528,7 @@
       <c r="G22" s="108"/>
       <c r="H22" s="50"/>
     </row>
-    <row r="23" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" ht="75">
       <c r="B23" s="50" t="s">
         <v>504</v>
       </c>
@@ -14547,7 +14547,7 @@
       <c r="G23" s="114"/>
       <c r="H23" s="50"/>
     </row>
-    <row r="24" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" ht="75">
       <c r="B24" s="50" t="s">
         <v>504</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" ht="75">
       <c r="B25" s="56" t="s">
         <v>504</v>
       </c>
@@ -14589,7 +14589,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="75">
       <c r="B26" s="50" t="s">
         <v>504</v>
       </c>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="H26" s="55"/>
     </row>
-    <row r="27" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" ht="75">
       <c r="B27" s="50" t="s">
         <v>504</v>
       </c>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="H27" s="55"/>
     </row>
-    <row r="28" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" ht="75">
       <c r="B28" s="50" t="s">
         <v>504</v>
       </c>
@@ -14650,7 +14650,7 @@
       <c r="G28" s="108"/>
       <c r="H28" s="55"/>
     </row>
-    <row r="29" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" ht="75">
       <c r="B29" s="50" t="s">
         <v>504</v>
       </c>
@@ -14669,7 +14669,7 @@
       <c r="G29" s="108"/>
       <c r="H29" s="55"/>
     </row>
-    <row r="30" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" ht="75">
       <c r="B30" s="50" t="s">
         <v>504</v>
       </c>
@@ -14688,7 +14688,7 @@
       <c r="G30" s="108"/>
       <c r="H30" s="55"/>
     </row>
-    <row r="31" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" ht="75">
       <c r="B31" s="56" t="s">
         <v>504</v>
       </c>
@@ -14707,7 +14707,7 @@
       <c r="G31" s="50"/>
       <c r="H31" s="50"/>
     </row>
-    <row r="32" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" ht="75">
       <c r="B32" s="50" t="s">
         <v>504</v>
       </c>
@@ -14726,7 +14726,7 @@
       <c r="G32" s="50"/>
       <c r="H32" s="50"/>
     </row>
-    <row r="33" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" ht="75">
       <c r="B33" s="50" t="s">
         <v>504</v>
       </c>
@@ -14745,7 +14745,7 @@
       <c r="G33" s="50"/>
       <c r="H33" s="50"/>
     </row>
-    <row r="34" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" ht="75">
       <c r="B34" s="50" t="s">
         <v>504</v>
       </c>
@@ -14764,7 +14764,7 @@
       <c r="G34" s="50"/>
       <c r="H34" s="50"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8">
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="21"/>
@@ -14772,7 +14772,7 @@
       <c r="F35" s="21"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8">
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
       <c r="D36" s="21"/>
@@ -14780,7 +14780,7 @@
       <c r="F36" s="21"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8">
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
       <c r="D37" s="21"/>
@@ -14788,7 +14788,7 @@
       <c r="F37" s="21"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8">
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
       <c r="D38" s="21"/>
@@ -14796,7 +14796,7 @@
       <c r="F38" s="21"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8">
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
@@ -14804,7 +14804,7 @@
       <c r="F39" s="21"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8">
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
@@ -14812,7 +14812,7 @@
       <c r="F40" s="21"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8">
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
@@ -14820,7 +14820,7 @@
       <c r="F41" s="21"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8">
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
@@ -14828,7 +14828,7 @@
       <c r="F42" s="21"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8">
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
@@ -14836,7 +14836,7 @@
       <c r="F43" s="21"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8">
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
@@ -14844,7 +14844,7 @@
       <c r="F44" s="21"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8">
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -14852,7 +14852,7 @@
       <c r="F45" s="21"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8">
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -14860,7 +14860,7 @@
       <c r="F46" s="21"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8">
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -14868,7 +14868,7 @@
       <c r="F47" s="21"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8">
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
@@ -14876,7 +14876,7 @@
       <c r="F48" s="21"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7">
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
@@ -14884,7 +14884,7 @@
       <c r="F49" s="21"/>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7">
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
@@ -14892,7 +14892,7 @@
       <c r="F50" s="21"/>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7">
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
@@ -14900,7 +14900,7 @@
       <c r="F51" s="21"/>
       <c r="G51" s="2"/>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7">
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
@@ -14908,7 +14908,7 @@
       <c r="F52" s="21"/>
       <c r="G52" s="2"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7">
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
@@ -14916,7 +14916,7 @@
       <c r="F53" s="21"/>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7">
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
@@ -14924,7 +14924,7 @@
       <c r="F54" s="21"/>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7">
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
@@ -14932,7 +14932,7 @@
       <c r="F55" s="21"/>
       <c r="G55" s="2"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7">
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
@@ -14950,45 +14950,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c5c85ca9-75e2-4cbf-9943-c4ded903b9d8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e0686363-9f0c-47fb-ae02-12d072ae143b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="c5c85ca9-75e2-4cbf-9943-c4ded903b9d8">
-      <UserInfo>
-        <DisplayName>Mali McCutcheon</DisplayName>
-        <AccountId>4245</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Laura Scheetz</DisplayName>
-        <AccountId>662</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kelham Cliffe</DisplayName>
-        <AccountId>3970</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006363DC14358BDE418DB8344B55CF6411" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="338cd0572d42505aa56fbc56ad96bb04">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="e0686363-9f0c-47fb-ae02-12d072ae143b" xmlns:ns3="c5c85ca9-75e2-4cbf-9943-c4ded903b9d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6373a4d9e5d137b00b2ce6a99a315c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -15260,42 +15221,53 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c5c85ca9-75e2-4cbf-9943-c4ded903b9d8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e0686363-9f0c-47fb-ae02-12d072ae143b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="c5c85ca9-75e2-4cbf-9943-c4ded903b9d8">
+      <UserInfo>
+        <DisplayName>Mali McCutcheon</DisplayName>
+        <AccountId>4245</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Laura Scheetz</DisplayName>
+        <AccountId>662</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kelham Cliffe</DisplayName>
+        <AccountId>3970</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6888317B-EA56-493D-9204-D3E3ADFF68DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c5c85ca9-75e2-4cbf-9943-c4ded903b9d8"/>
-    <ds:schemaRef ds:uri="e0686363-9f0c-47fb-ae02-12d072ae143b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DBB6258-F94D-4A70-ABAD-4D8F570C49D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3134C554-71BA-4DCA-B23E-4CED9F78578F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3134C554-71BA-4DCA-B23E-4CED9F78578F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DBB6258-F94D-4A70-ABAD-4D8F570C49D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="e0686363-9f0c-47fb-ae02-12d072ae143b"/>
-    <ds:schemaRef ds:uri="c5c85ca9-75e2-4cbf-9943-c4ded903b9d8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6888317B-EA56-493D-9204-D3E3ADFF68DA}"/>
 </file>